--- a/public/files/Д-т К-т 01.08.2026.xlsx
+++ b/public/files/Д-т К-т 01.08.2026.xlsx
@@ -590,20 +590,20 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -715,7 +715,10 @@
       <sheetName val="15.07.2026 тэс опер.с Тах"/>
       <sheetName val="22.07.2026 тэс опер.с Тах "/>
       <sheetName val="29.07.2026 тэс опер.с Тах"/>
+      <sheetName val="01.08.2026 тэс опер.без Ново-Ан"/>
+      <sheetName val="01.07.2026 тэс опер.без Ново-ан"/>
       <sheetName val="01.08.2026 тэс опер.с Тах"/>
+      <sheetName val="12.08.2026 тэс опер.с Тах "/>
       <sheetName val="д-т к-т на 1.11.   с пен (7)"/>
     </sheetNames>
     <sheetDataSet>
@@ -920,6 +923,9 @@
       <sheetData sheetId="86"/>
       <sheetData sheetId="87"/>
       <sheetData sheetId="88"/>
+      <sheetData sheetId="89"/>
+      <sheetData sheetId="90"/>
+      <sheetData sheetId="91"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1257,28 +1263,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="93" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
       <c r="U1" s="1"/>
     </row>
     <row r="2" spans="1:59" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -1310,22 +1316,22 @@
       <c r="F3" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="69" t="s">
+      <c r="G3" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="69"/>
-      <c r="T3" s="69"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
       <c r="U3" s="64"/>
     </row>
     <row r="4" spans="1:59" ht="141" customHeight="1" x14ac:dyDescent="0.45">
@@ -1392,15 +1398,15 @@
       </c>
       <c r="D5" s="15">
         <f>D6+D9+D15+D16+D17+D14</f>
-        <v>5665172.7695188895</v>
+        <v>5653345.7695188895</v>
       </c>
       <c r="E5" s="15">
         <f>E6+E9+E15+E16+E17+E14</f>
-        <v>-2148027.23848111</v>
+        <v>-2159854.23848111</v>
       </c>
       <c r="F5" s="15">
         <f t="shared" ref="F5" si="0">F6+F9+F15+F16+F17</f>
-        <v>-2196862.1229622196</v>
+        <v>-2191930.7229622197</v>
       </c>
       <c r="G5" s="15">
         <f>G6+G9+G15+G16+G17+G14</f>
@@ -1432,7 +1438,7 @@
       </c>
       <c r="N5" s="15">
         <f t="shared" si="1"/>
-        <v>172618.19</v>
+        <v>158150.39000000001</v>
       </c>
       <c r="O5" s="15">
         <f t="shared" si="1"/>
@@ -1456,7 +1462,7 @@
       </c>
       <c r="T5" s="15">
         <f t="shared" si="1"/>
-        <v>243144.9</v>
+        <v>245785.7</v>
       </c>
       <c r="U5" s="15">
         <f t="shared" si="1"/>
@@ -1476,15 +1482,15 @@
       </c>
       <c r="D6" s="15">
         <f>D7+D8+D10+D11+D12+D13</f>
-        <v>1763954.2709188899</v>
+        <v>1749565.3709188898</v>
       </c>
       <c r="E6" s="15">
         <f t="shared" ref="E6:U6" si="2">E7+E8+E10+E11+E12+E13</f>
-        <v>-807279.47808111017</v>
+        <v>-821668.37808111019</v>
       </c>
       <c r="F6" s="15">
         <f t="shared" si="2"/>
-        <v>-1019535.9625622197</v>
+        <v>-1019378.1625622199</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="2"/>
@@ -1516,7 +1522,7 @@
       </c>
       <c r="N6" s="15">
         <f t="shared" si="2"/>
-        <v>172618.19</v>
+        <v>158150.39000000001</v>
       </c>
       <c r="O6" s="15">
         <f t="shared" si="2"/>
@@ -1540,7 +1546,7 @@
       </c>
       <c r="T6" s="15">
         <f t="shared" si="2"/>
-        <v>87279.5</v>
+        <v>87358.399999999994</v>
       </c>
       <c r="U6" s="15">
         <f t="shared" si="2"/>
@@ -1560,15 +1566,15 @@
       </c>
       <c r="D7" s="17">
         <f t="shared" ref="D7:D17" si="3">SUM(G7:U7)</f>
-        <v>1183655.3899999999</v>
+        <v>1169187.5899999999</v>
       </c>
       <c r="E7" s="17">
         <f t="shared" ref="E7:E17" si="4">SUM(D7-C7)</f>
-        <v>-829481.88000000012</v>
+        <v>-843949.68000000017</v>
       </c>
       <c r="F7" s="17">
         <f>F8+F9+F11+F12+F13+F15</f>
-        <v>-1041738.3644811098</v>
+        <v>-1041659.4644811099</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="49">
@@ -1582,7 +1588,7 @@
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="N7" s="18">
-        <v>172618.19</v>
+        <v>158150.39000000001</v>
       </c>
       <c r="O7" s="18"/>
       <c r="P7" s="19"/>
@@ -1643,15 +1649,15 @@
       </c>
       <c r="D8" s="23">
         <f t="shared" si="3"/>
-        <v>1197.0809188899998</v>
+        <v>1470.0809188899998</v>
       </c>
       <c r="E8" s="23">
         <f t="shared" si="4"/>
-        <v>-9658.7900811099989</v>
+        <v>-9385.7900811099989</v>
       </c>
       <c r="F8" s="23">
         <f t="shared" ref="F8:F17" si="5">SUM(D8-C8)</f>
-        <v>-9658.7900811099989</v>
+        <v>-9385.7900811099989</v>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="24">
@@ -1674,7 +1680,9 @@
       <c r="Q8" s="26"/>
       <c r="R8" s="26"/>
       <c r="S8" s="26"/>
-      <c r="T8" s="24"/>
+      <c r="T8" s="24">
+        <v>273</v>
+      </c>
       <c r="U8" s="24"/>
       <c r="V8" s="16"/>
       <c r="X8" s="27"/>
@@ -1835,15 +1843,15 @@
       </c>
       <c r="D11" s="23">
         <f t="shared" si="3"/>
-        <v>47037</v>
+        <v>46842.899999999994</v>
       </c>
       <c r="E11" s="23">
         <f t="shared" si="4"/>
-        <v>-54091.41</v>
+        <v>-54285.510000000009</v>
       </c>
       <c r="F11" s="23">
         <f t="shared" si="5"/>
-        <v>-54091.41</v>
+        <v>-54285.510000000009</v>
       </c>
       <c r="G11" s="29">
         <v>0</v>
@@ -1867,7 +1875,7 @@
       <c r="R11" s="26"/>
       <c r="S11" s="26"/>
       <c r="T11" s="30">
-        <v>26762.9</v>
+        <v>26568.799999999999</v>
       </c>
       <c r="U11" s="24"/>
       <c r="V11" s="16"/>
@@ -1987,11 +1995,11 @@
       </c>
       <c r="D14" s="34">
         <f t="shared" si="3"/>
-        <v>1787599.6</v>
+        <v>1785387.9000000001</v>
       </c>
       <c r="E14" s="34">
         <f t="shared" si="4"/>
-        <v>-163421.59999999986</v>
+        <v>-165633.29999999981</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="35"/>
@@ -2012,7 +2020,7 @@
       <c r="R14" s="35"/>
       <c r="S14" s="35"/>
       <c r="T14" s="35">
-        <v>126004</v>
+        <v>123792.3</v>
       </c>
       <c r="U14" s="35"/>
       <c r="V14" s="37"/>
@@ -2116,15 +2124,15 @@
       </c>
       <c r="D16" s="23">
         <f t="shared" si="3"/>
-        <v>67933.8</v>
+        <v>72707.400000000009</v>
       </c>
       <c r="E16" s="23">
         <f t="shared" si="4"/>
-        <v>-62814.2</v>
+        <v>-58040.599999999991</v>
       </c>
       <c r="F16" s="23">
         <f t="shared" si="5"/>
-        <v>-62814.2</v>
+        <v>-58040.599999999991</v>
       </c>
       <c r="G16" s="26">
         <v>0</v>
@@ -2150,7 +2158,7 @@
       <c r="R16" s="26"/>
       <c r="S16" s="26"/>
       <c r="T16" s="24">
-        <v>934</v>
+        <v>5707.6</v>
       </c>
       <c r="U16" s="24"/>
       <c r="V16" s="16"/>
@@ -2372,22 +2380,22 @@
       <c r="F21" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="69" t="s">
+      <c r="G21" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="69"/>
-      <c r="M21" s="69"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="69"/>
-      <c r="P21" s="69"/>
-      <c r="Q21" s="69"/>
-      <c r="R21" s="69"/>
-      <c r="S21" s="69"/>
-      <c r="T21" s="69"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="65"/>
+      <c r="S21" s="65"/>
+      <c r="T21" s="65"/>
       <c r="U21" s="64"/>
     </row>
     <row r="22" spans="1:59" ht="137.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2456,15 +2464,15 @@
       </c>
       <c r="D23" s="15">
         <f>D24+D27+D33+D34+D35+D32</f>
-        <v>2015936.670436</v>
+        <v>2017521.1734359998</v>
       </c>
       <c r="E23" s="15">
         <f t="shared" ref="E23:U23" si="6">E24+E27+E33+E34+E35+E32</f>
-        <v>-249478.03956399974</v>
+        <v>-247893.53656399978</v>
       </c>
       <c r="F23" s="15">
         <f t="shared" si="6"/>
-        <v>128758.67887200024</v>
+        <v>124741.98187200016</v>
       </c>
       <c r="G23" s="15">
         <f t="shared" si="6"/>
@@ -2492,7 +2500,7 @@
       </c>
       <c r="M23" s="15">
         <f t="shared" si="6"/>
-        <v>70539.199999999997</v>
+        <v>70590.2</v>
       </c>
       <c r="N23" s="15">
         <f t="shared" si="6"/>
@@ -2504,7 +2512,7 @@
       </c>
       <c r="P23" s="15">
         <f t="shared" si="6"/>
-        <v>253430.09900000002</v>
+        <v>249574.60200000001</v>
       </c>
       <c r="Q23" s="15">
         <f t="shared" si="6"/>
@@ -2520,7 +2528,7 @@
       </c>
       <c r="T23" s="15">
         <f>T24+T27+T33+T34+T35+T32</f>
-        <v>433246.6</v>
+        <v>438635.6</v>
       </c>
       <c r="U23" s="15">
         <f t="shared" si="6"/>
@@ -2539,15 +2547,15 @@
       </c>
       <c r="D24" s="15">
         <f t="shared" ref="D24:T24" si="7">D25+D26+D28+D29+D30+D31</f>
-        <v>94461.754436000003</v>
+        <v>89467.654436000012</v>
       </c>
       <c r="E24" s="15">
         <f t="shared" si="7"/>
-        <v>-307330.63156399998</v>
+        <v>-312324.73156399996</v>
       </c>
       <c r="F24" s="15">
         <f t="shared" si="7"/>
-        <v>29827.436871999991</v>
+        <v>19890.236872000001</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="7"/>
@@ -2603,7 +2611,7 @@
       </c>
       <c r="T24" s="15">
         <f t="shared" si="7"/>
-        <v>85252.7</v>
+        <v>80258.600000000006</v>
       </c>
       <c r="U24" s="15">
         <f>U25+U26+U28+U29+U30+U31</f>
@@ -2630,7 +2638,7 @@
       </c>
       <c r="F25" s="17">
         <f>F26+F27+F29+F30+F31+F33</f>
-        <v>-11573.43156400001</v>
+        <v>-16516.531564000004</v>
       </c>
       <c r="G25" s="49"/>
       <c r="H25" s="49"/>
@@ -2705,15 +2713,15 @@
       </c>
       <c r="D26" s="17">
         <f>SUM(G26:U26)</f>
-        <v>22744.118000000002</v>
+        <v>25490.118000000002</v>
       </c>
       <c r="E26" s="17">
         <f>SUM(D26-C26)</f>
-        <v>-2692.7189999999973</v>
+        <v>53.281000000002678</v>
       </c>
       <c r="F26" s="17">
         <f t="shared" ref="F26:F34" si="9">D26-C26</f>
-        <v>-2692.7189999999973</v>
+        <v>53.281000000002678</v>
       </c>
       <c r="G26" s="26"/>
       <c r="H26" s="26">
@@ -2739,7 +2747,7 @@
         <v>5140.518</v>
       </c>
       <c r="T26" s="29">
-        <v>17603</v>
+        <v>20349</v>
       </c>
       <c r="U26" s="26">
         <v>0</v>
@@ -3003,15 +3011,15 @@
       </c>
       <c r="D31" s="17">
         <f t="shared" si="10"/>
-        <v>33979.962999999996</v>
+        <v>26239.863000000001</v>
       </c>
       <c r="E31" s="17">
         <f t="shared" si="8"/>
-        <v>27937.451999999997</v>
+        <v>20197.352000000003</v>
       </c>
       <c r="F31" s="17">
         <f t="shared" si="9"/>
-        <v>27937.451999999997</v>
+        <v>20197.352000000003</v>
       </c>
       <c r="G31" s="26">
         <v>511.9</v>
@@ -3033,7 +3041,7 @@
         <v>1001.963</v>
       </c>
       <c r="T31" s="29">
-        <v>32466.1</v>
+        <v>24726</v>
       </c>
       <c r="U31" s="26">
         <v>0</v>
@@ -3054,11 +3062,11 @@
       </c>
       <c r="D32" s="33">
         <f t="shared" si="10"/>
-        <v>68278.099999999991</v>
+        <v>68936.2</v>
       </c>
       <c r="E32" s="33">
         <f t="shared" si="8"/>
-        <v>-41078.650000000009</v>
+        <v>-40420.550000000003</v>
       </c>
       <c r="F32" s="33"/>
       <c r="G32" s="35">
@@ -3079,7 +3087,7 @@
       <c r="R32" s="35"/>
       <c r="S32" s="35"/>
       <c r="T32" s="50">
-        <v>31496.3</v>
+        <v>32154.400000000001</v>
       </c>
       <c r="U32" s="35">
         <v>0.2</v>
@@ -3100,15 +3108,15 @@
       </c>
       <c r="D33" s="17">
         <f t="shared" si="10"/>
-        <v>211082.56</v>
+        <v>211133.56</v>
       </c>
       <c r="E33" s="17">
         <f>SUM(D33-C33)</f>
-        <v>-26287.200000000012</v>
+        <v>-26236.200000000012</v>
       </c>
       <c r="F33" s="17">
         <f t="shared" si="9"/>
-        <v>-26287.200000000012</v>
+        <v>-26236.200000000012</v>
       </c>
       <c r="G33" s="26">
         <v>1719.8</v>
@@ -3123,7 +3131,7 @@
       <c r="K33" s="40"/>
       <c r="L33" s="40"/>
       <c r="M33" s="26">
-        <v>70539.199999999997</v>
+        <v>70590.2</v>
       </c>
       <c r="N33" s="40">
         <v>118136.66</v>
@@ -3191,15 +3199,15 @@
       </c>
       <c r="D34" s="17">
         <f t="shared" si="10"/>
-        <v>325231.01199999999</v>
+        <v>327846.11199999996</v>
       </c>
       <c r="E34" s="17">
         <f t="shared" si="8"/>
-        <v>-45989.108999999997</v>
+        <v>-43374.00900000002</v>
       </c>
       <c r="F34" s="17">
         <f t="shared" si="9"/>
-        <v>-45989.108999999997</v>
+        <v>-43374.00900000002</v>
       </c>
       <c r="G34" s="26">
         <v>23.5</v>
@@ -3217,7 +3225,7 @@
       </c>
       <c r="O34" s="40"/>
       <c r="P34" s="26">
-        <v>18860.2</v>
+        <v>15616.7</v>
       </c>
       <c r="Q34" s="26"/>
       <c r="R34" s="26"/>
@@ -3225,7 +3233,7 @@
         <v>56.012</v>
       </c>
       <c r="T34" s="29">
-        <v>103234</v>
+        <v>109092.6</v>
       </c>
       <c r="U34" s="26">
         <v>17359.5</v>
@@ -3282,15 +3290,15 @@
       </c>
       <c r="D35" s="17">
         <f t="shared" si="10"/>
-        <v>1316563.344</v>
+        <v>1319817.747</v>
       </c>
       <c r="E35" s="17">
         <f t="shared" si="8"/>
-        <v>177545.35100000026</v>
+        <v>180799.75400000019</v>
       </c>
       <c r="F35" s="23">
         <f>SUM(D35-C35)</f>
-        <v>177545.35100000026</v>
+        <v>180799.75400000019</v>
       </c>
       <c r="G35" s="26"/>
       <c r="H35" s="26">
@@ -3310,8 +3318,8 @@
       <c r="N35" s="40"/>
       <c r="O35" s="40"/>
       <c r="P35" s="40">
-        <f>43638.479+9239.069+178355.391+3336.96</f>
-        <v>234569.899</v>
+        <f>43026.852+9239.069+178355.391+3336.59</f>
+        <v>233957.902</v>
       </c>
       <c r="Q35" s="26"/>
       <c r="R35" s="26"/>
@@ -3319,7 +3327,7 @@
         <v>18825.945</v>
       </c>
       <c r="T35" s="29">
-        <v>200028.5</v>
+        <v>203894.9</v>
       </c>
       <c r="U35" s="26">
         <v>2423.8000000000002</v>
@@ -3406,13 +3414,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="G21:T21"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -3421,6 +3422,13 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:T3"/>
+    <mergeCell ref="G21:T21"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
